--- a/dados/excel/unidade_top20.xlsx
+++ b/dados/excel/unidade_top20.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$21</definedName>
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/unidade_top20.xlsx
+++ b/dados/excel/unidade_top20.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>EM Ines R. Cesarotti</t>
+          <t>CEI 109 — Benedicto Pagl</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1214,19 +1214,19 @@
         <v>60</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>623472</v>
+        <v>429708.28</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>10391.2</v>
+        <v>7161.804666666666</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>10391.2</v>
+        <v>7161.804666666666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>CEI 109 — Benedicto Pagl</t>
+          <t>EM Ines R. Cesarotti</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -1238,13 +1238,13 @@
         <v>60</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>429708.28</v>
+        <v>623472</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>7161.804666666666</v>
+        <v>10391.2</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>7161.804666666666</v>
+        <v>10391.2</v>
       </c>
     </row>
     <row r="20">
@@ -1274,7 +1274,7 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>EM Achilles Almeida</t>
+          <t>EM Benedito Cleto</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -1286,13 +1286,13 @@
         <v>57</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>680971.87</v>
+        <v>503701.83</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>11946.8749122807</v>
+        <v>8836.874210526315</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>11946.8749122807</v>
+        <v>8836.874210526315</v>
       </c>
     </row>
   </sheetData>
